--- a/service_group.xlsx
+++ b/service_group.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\상수\Desktop\서비스자원검색\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정상수\Desktop\서비스자원검색(260318)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13965"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,10 +58,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>의료처치(욕창, 루, 튜부관리 등)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>감염관리</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -139,10 +135,6 @@
   </si>
   <si>
     <t>AI-IOT 건강관리</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문건건강관리</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1638,6 +1630,14 @@
   </si>
   <si>
     <t>위 내용에 포함하지 않은 통합돌봄  서비스를 알고싶다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>의료처치(욕창, 루, 튜브관리 등)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문건강관리</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2363,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
@@ -2383,10 +2383,10 @@
         <v>4</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
@@ -2400,10 +2400,10 @@
         <v>5</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
@@ -2417,10 +2417,10 @@
         <v>6</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2434,10 +2434,10 @@
         <v>7</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
@@ -2448,13 +2448,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>8</v>
+        <v>344</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2465,13 +2465,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2482,13 +2482,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
@@ -2499,13 +2499,13 @@
         <v>3</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I9" s="2"/>
     </row>
@@ -2514,16 +2514,16 @@
         <v>2</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>13</v>
-      </c>
       <c r="D10" s="12" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2531,16 +2531,16 @@
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
@@ -2548,16 +2548,16 @@
         <v>2</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2565,16 +2565,16 @@
         <v>2</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>16</v>
-      </c>
       <c r="D13" s="12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2582,16 +2582,16 @@
         <v>2</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2599,16 +2599,16 @@
         <v>2</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2616,16 +2616,16 @@
         <v>2</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -2633,16 +2633,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -2650,16 +2650,16 @@
         <v>2</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -2667,16 +2667,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -2684,16 +2684,16 @@
         <v>2</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -2701,16 +2701,16 @@
         <v>2</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
@@ -2718,1648 +2718,1648 @@
         <v>2</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" s="18" t="s">
         <v>165</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>166</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>25</v>
-      </c>
       <c r="D30" s="12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>29</v>
+        <v>345</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B37" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C37" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="D37" s="12" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>37</v>
-      </c>
       <c r="D42" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B50" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C50" s="12" t="s">
-        <v>45</v>
-      </c>
       <c r="D50" s="12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B55" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>50</v>
-      </c>
       <c r="D55" s="12" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B56" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C56" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="D56" s="12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B60" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="12" t="s">
-        <v>13</v>
-      </c>
       <c r="D60" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B63" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C63" s="12" t="s">
-        <v>57</v>
-      </c>
       <c r="D63" s="12" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B64" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>50</v>
-      </c>
       <c r="D64" s="12" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B66" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>60</v>
-      </c>
       <c r="D66" s="12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B68" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>50</v>
-      </c>
       <c r="D68" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B73" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C73" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>65</v>
-      </c>
       <c r="D73" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C76" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B76" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C76" s="12" t="s">
-        <v>69</v>
-      </c>
       <c r="D76" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B77" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C77" s="12" t="s">
-        <v>70</v>
-      </c>
       <c r="D77" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A81" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B83" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C83" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="C83" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="D83" s="12" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A86" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A87" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B87" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C87" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="C87" s="12" t="s">
-        <v>80</v>
-      </c>
       <c r="D87" s="12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A89" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E89" s="18" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B90" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>83</v>
-      </c>
       <c r="D90" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B94" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C94" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C94" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="D94" s="12" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A97" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B97" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E98" s="18" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C100" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B100" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C100" s="12" t="s">
-        <v>93</v>
-      </c>
       <c r="D100" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B101" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C101" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C101" s="12" t="s">
-        <v>94</v>
-      </c>
       <c r="D101" s="12" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B105" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C105" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C105" s="12" t="s">
-        <v>98</v>
-      </c>
       <c r="D105" s="12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E107" s="18" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E109" s="18" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E111" s="18" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E112" s="18" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C113" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C113" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="D113" s="12" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E113" s="18" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E114" s="18" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E115" s="18" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B116" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C116" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C116" s="12" t="s">
-        <v>107</v>
-      </c>
       <c r="D116" s="12" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E117" s="18" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/service_group.xlsx
+++ b/service_group.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정상수\Desktop\서비스자원검색(260318)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\상수\Desktop\서비스자원검색\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$118</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -558,30 +561,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>혼자 사는 어르신인데 건강 상태를 전반적으로 평가받고 싶다
-퇴원 후 집에서 생활하려는데 의료 평가가 필요하다
-여러 질환이 있어 방문진료로 건강 상태를 확인하고 싶다
-어르신 건강 상태를 종합적으로 확인하고 돌봄 계획을 세우고 싶다
-집에서 의사가 건강 상태를 평가해주면 좋겠다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>당뇨가 있는 어르신이라 건강 관리 상담이 필요하다
-질병 관리 방법을 의사에게 상담받고 싶다
-어르신 건강 관리 방법에 대해 상담이 필요하다
-병원 방문이 어려워 집에서 상담을 받고 싶다
-보호자가 질환 관리 방법을 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>어르신이 먹는 약이 너무 많아 줄일 수 있는지 상담이 필요하다
-약 부작용이 있어 약을 조정하고 싶다
-병원 가기 어려워 집에서 약 처방을 받고 싶다
-현재 복용 중인 약이 맞는지 의사가 확인해주면 좋겠다
-고령이라 약을 줄이는 탈처방 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신 독감 예방접종을 집에서 받을 수 있을까
 거동이 어려워 방문 예방접종이 필요하다
 폐렴 예방접종 상담이 필요하다
@@ -617,13 +596,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>당뇨가 있는 혼자 사는 어르신이라 혈당 관리가 필요하다
-고혈압이 있어 정기적으로 건강 상태 확인이 필요하다
-만성질환이 있어 방문 간호 건강 관리가 필요하다
-어르신 건강 상태를 정기적으로 체크해 줄 사람이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신 기본 간호가 필요하다
 병원 퇴원 후 간호 관리가 필요하다
 환자 상태를 관리해 줄 간호 서비스가 필요하다
@@ -1223,13 +1195,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 목욕을 혼자 하기 어려워 도움을 받고 싶다
-거동이 불편해 세수나 목욕을 도와줄 사람이 필요하다
-몸이 불편한 어르신 위생 관리 지원이 필요하다
-어르신 목욕을 시켜드리기 어려운 상황이다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>일상생활돌봄 서비스로 돌봄 인력이 방문하여 어르신의 옷 갈아입기 등 개인 생활 활동을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1638,6 +1603,40 @@
   </si>
   <si>
     <t>방문건강관리</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>질병 관리 방법을 의사에게 상담받고 싶다
+어르신 건강 관리 방법에 대해 상담이 필요하다
+병원 방문이 어려워 집에서 상담을 받고 싶다
+보호자가 질환 관리 방법을 알고 싶다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>먹는 약이 너무 많아 상담이 필요하다
+거동이 불편해  집에서 약 처방을 받고 싶다
+현재 복용 중인 약이 맞는지 의사가 확인해주면 좋겠다
+고령이라 약을 줄이는 탈처방 상담이 필요하다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>당뇨가, 고혈압이 있어 정기적으로 건강 상태 확인이 필요하다
+만성질환이 있어 방문 간호 건강 관리가 필요하다
+어르신 건강 상태를 정기적으로 체크해 줄 사람이 필요하다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>어르신 목욕을 혼자 하기 어렵다
+거동이 불편해 세수나 목욕을 도와줄 사람이 필요하다
+거동이 불편한 어르신 위생 관리 지원이 필요하다
+어르신 목욕을 시켜드리기 어려운 상황이다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강 상태 전반을 평가받고 싶다
+질환으로 방문진료를 활용한 건강 상태를 확인하고 싶다
+건강 상태의 종합적 확인 및 돌봄 계획을 세우고 싶다
+집에서 의사가 건강을 평가해주면 좋겠다</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2371,8 +2370,11 @@
       <c r="E1" s="22" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="F1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="66" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -2386,10 +2388,14 @@
         <v>112</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+        <v>345</v>
+      </c>
+      <c r="F2">
+        <f>LEN(E2)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="66" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2403,10 +2409,14 @@
         <v>113</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="0">LEN(E3)</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -2420,7 +2430,11 @@
         <v>114</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>135</v>
+        <v>342</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2437,7 +2451,11 @@
         <v>115</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
@@ -2448,13 +2466,17 @@
         <v>3</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>116</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>138</v>
+        <v>135</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2471,7 +2493,11 @@
         <v>117</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>137</v>
+        <v>134</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2488,7 +2514,11 @@
         <v>118</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>139</v>
+        <v>136</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
@@ -2505,11 +2535,15 @@
         <v>119</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>140</v>
+        <v>137</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>74</v>
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>2</v>
       </c>
@@ -2523,7 +2557,11 @@
         <v>120</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>141</v>
+        <v>343</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2540,7 +2578,11 @@
         <v>121</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>142</v>
+        <v>138</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
@@ -2557,7 +2599,11 @@
         <v>122</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>143</v>
+        <v>139</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2574,7 +2620,11 @@
         <v>123</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2591,7 +2641,11 @@
         <v>124</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2608,7 +2662,11 @@
         <v>125</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>146</v>
+        <v>142</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="66" x14ac:dyDescent="0.3">
@@ -2625,10 +2683,14 @@
         <v>126</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>2</v>
       </c>
@@ -2642,10 +2704,14 @@
         <v>127</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>2</v>
       </c>
@@ -2659,10 +2725,14 @@
         <v>128</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>2</v>
       </c>
@@ -2676,10 +2746,14 @@
         <v>129</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>2</v>
       </c>
@@ -2693,10 +2767,14 @@
         <v>130</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>2</v>
       </c>
@@ -2710,10 +2788,14 @@
         <v>131</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>2</v>
       </c>
@@ -2727,10 +2809,14 @@
         <v>132</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>23</v>
       </c>
@@ -2741,13 +2827,17 @@
         <v>15</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>23</v>
       </c>
@@ -2758,13 +2848,17 @@
         <v>5</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
@@ -2775,13 +2869,17 @@
         <v>10</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>23</v>
       </c>
@@ -2792,13 +2890,17 @@
         <v>15</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>156</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>23</v>
       </c>
@@ -2809,13 +2911,17 @@
         <v>5</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>23</v>
       </c>
@@ -2826,13 +2932,17 @@
         <v>10</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>23</v>
       </c>
@@ -2843,13 +2953,17 @@
         <v>15</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>23</v>
       </c>
@@ -2860,13 +2974,17 @@
         <v>24</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>23</v>
       </c>
@@ -2877,13 +2995,17 @@
         <v>25</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>23</v>
       </c>
@@ -2894,13 +3016,17 @@
         <v>26</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>23</v>
       </c>
@@ -2911,13 +3037,17 @@
         <v>27</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>23</v>
       </c>
@@ -2925,16 +3055,20 @@
         <v>12</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>23</v>
       </c>
@@ -2945,13 +3079,17 @@
         <v>10</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>174</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>23</v>
       </c>
@@ -2962,13 +3100,17 @@
         <v>29</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>23</v>
       </c>
@@ -2979,13 +3121,17 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>23</v>
       </c>
@@ -2996,13 +3142,17 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>23</v>
       </c>
@@ -3013,13 +3163,17 @@
         <v>32</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>23</v>
       </c>
@@ -3030,13 +3184,17 @@
         <v>10</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>23</v>
       </c>
@@ -3047,13 +3205,17 @@
         <v>34</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>23</v>
       </c>
@@ -3064,13 +3226,17 @@
         <v>35</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>23</v>
       </c>
@@ -3081,13 +3247,17 @@
         <v>36</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>23</v>
       </c>
@@ -3098,13 +3268,17 @@
         <v>37</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>23</v>
       </c>
@@ -3115,13 +3289,17 @@
         <v>38</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>23</v>
       </c>
@@ -3132,13 +3310,17 @@
         <v>39</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>23</v>
       </c>
@@ -3149,13 +3331,17 @@
         <v>40</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="10" t="s">
         <v>23</v>
       </c>
@@ -3166,13 +3352,17 @@
         <v>10</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>23</v>
       </c>
@@ -3183,13 +3373,17 @@
         <v>42</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>23</v>
       </c>
@@ -3200,13 +3394,17 @@
         <v>43</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>23</v>
       </c>
@@ -3217,13 +3415,17 @@
         <v>44</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>23</v>
       </c>
@@ -3234,13 +3436,17 @@
         <v>45</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>23</v>
       </c>
@@ -3251,13 +3457,17 @@
         <v>10</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>23</v>
       </c>
@@ -3268,13 +3478,17 @@
         <v>10</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>46</v>
       </c>
@@ -3285,13 +3499,17 @@
         <v>48</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>46</v>
       </c>
@@ -3302,13 +3520,17 @@
         <v>49</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>46</v>
       </c>
@@ -3319,13 +3541,17 @@
         <v>50</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>46</v>
       </c>
@@ -3336,13 +3562,17 @@
         <v>51</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>46</v>
       </c>
@@ -3353,13 +3583,17 @@
         <v>52</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>46</v>
       </c>
@@ -3370,13 +3604,17 @@
         <v>12</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>46</v>
       </c>
@@ -3387,13 +3625,17 @@
         <v>13</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>46</v>
       </c>
@@ -3404,13 +3646,17 @@
         <v>54</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>46</v>
       </c>
@@ -3421,13 +3667,17 @@
         <v>55</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>46</v>
       </c>
@@ -3438,13 +3688,17 @@
         <v>48</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>46</v>
       </c>
@@ -3455,13 +3709,17 @@
         <v>57</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>46</v>
       </c>
@@ -3472,13 +3730,17 @@
         <v>58</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>46</v>
       </c>
@@ -3489,13 +3751,17 @@
         <v>59</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+      <c r="F67">
+        <f t="shared" ref="F67:F118" si="1">LEN(E67)</f>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>46</v>
       </c>
@@ -3506,13 +3772,17 @@
         <v>48</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>46</v>
       </c>
@@ -3523,13 +3793,17 @@
         <v>57</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>46</v>
       </c>
@@ -3540,13 +3814,17 @@
         <v>58</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>46</v>
       </c>
@@ -3557,13 +3835,17 @@
         <v>59</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>46</v>
       </c>
@@ -3574,13 +3856,17 @@
         <v>62</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
         <v>46</v>
       </c>
@@ -3591,13 +3877,17 @@
         <v>63</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
         <v>46</v>
       </c>
@@ -3608,13 +3898,17 @@
         <v>64</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>46</v>
       </c>
@@ -3625,13 +3919,17 @@
         <v>10</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>254</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>65</v>
       </c>
@@ -3642,13 +3940,17 @@
         <v>67</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>344</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
         <v>65</v>
       </c>
@@ -3659,13 +3961,17 @@
         <v>68</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
         <v>65</v>
       </c>
@@ -3676,13 +3982,17 @@
         <v>69</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
         <v>65</v>
       </c>
@@ -3693,13 +4003,17 @@
         <v>70</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>261</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
         <v>65</v>
       </c>
@@ -3710,13 +4024,17 @@
         <v>71</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A81" s="10" t="s">
         <v>65</v>
       </c>
@@ -3727,13 +4045,17 @@
         <v>10</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>65</v>
       </c>
@@ -3744,13 +4066,17 @@
         <v>73</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>267</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
         <v>65</v>
       </c>
@@ -3761,13 +4087,17 @@
         <v>74</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>65</v>
       </c>
@@ -3778,13 +4108,17 @@
         <v>75</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>271</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>65</v>
       </c>
@@ -3795,13 +4129,17 @@
         <v>10</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A86" s="10" t="s">
         <v>65</v>
       </c>
@@ -3812,13 +4150,17 @@
         <v>77</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A87" s="10" t="s">
         <v>65</v>
       </c>
@@ -3829,13 +4171,17 @@
         <v>78</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
         <v>65</v>
       </c>
@@ -3846,13 +4192,17 @@
         <v>10</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>279</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A89" s="10" t="s">
         <v>65</v>
       </c>
@@ -3863,13 +4213,17 @@
         <v>80</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E89" s="18" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
         <v>65</v>
       </c>
@@ -3880,13 +4234,17 @@
         <v>81</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>283</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
         <v>65</v>
       </c>
@@ -3897,13 +4255,17 @@
         <v>10</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
         <v>65</v>
       </c>
@@ -3914,13 +4276,17 @@
         <v>83</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
         <v>65</v>
       </c>
@@ -3931,13 +4297,17 @@
         <v>85</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
         <v>65</v>
       </c>
@@ -3948,13 +4318,17 @@
         <v>86</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>65</v>
       </c>
@@ -3965,13 +4339,17 @@
         <v>10</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
         <v>65</v>
       </c>
@@ -3982,13 +4360,17 @@
         <v>88</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="1"/>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A97" s="10" t="s">
         <v>65</v>
       </c>
@@ -3999,13 +4381,17 @@
         <v>51</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>297</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>65</v>
       </c>
@@ -4016,13 +4402,17 @@
         <v>10</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E98" s="18" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
         <v>65</v>
       </c>
@@ -4033,13 +4423,17 @@
         <v>10</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
         <v>89</v>
       </c>
@@ -4050,13 +4444,17 @@
         <v>91</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+        <v>303</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="66" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
         <v>89</v>
       </c>
@@ -4067,13 +4465,17 @@
         <v>92</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
         <v>89</v>
       </c>
@@ -4084,13 +4486,17 @@
         <v>93</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+      <c r="F102">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
         <v>89</v>
       </c>
@@ -4101,13 +4507,17 @@
         <v>10</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+      <c r="F103">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
         <v>89</v>
       </c>
@@ -4118,13 +4528,17 @@
         <v>95</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
         <v>89</v>
       </c>
@@ -4135,13 +4549,17 @@
         <v>96</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>312</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
         <v>89</v>
       </c>
@@ -4152,13 +4570,17 @@
         <v>10</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>89</v>
       </c>
@@ -4169,13 +4591,17 @@
         <v>10</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="E107" s="18" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>316</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
         <v>10</v>
       </c>
@@ -4186,13 +4612,17 @@
         <v>97</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
         <v>10</v>
       </c>
@@ -4203,13 +4633,17 @@
         <v>10</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E109" s="18" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>320</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
         <v>10</v>
       </c>
@@ -4220,13 +4654,17 @@
         <v>99</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
         <v>10</v>
       </c>
@@ -4237,13 +4675,17 @@
         <v>10</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="E111" s="18" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>324</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
         <v>10</v>
       </c>
@@ -4254,13 +4696,17 @@
         <v>101</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="E112" s="18" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+      <c r="F112">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
         <v>10</v>
       </c>
@@ -4271,13 +4717,17 @@
         <v>102</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="E113" s="18" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+      <c r="F113">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
         <v>10</v>
       </c>
@@ -4288,13 +4738,17 @@
         <v>10</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="E114" s="18" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>330</v>
+      </c>
+      <c r="F114">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
         <v>10</v>
       </c>
@@ -4305,13 +4759,17 @@
         <v>104</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E115" s="18" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+      <c r="F115">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
         <v>10</v>
       </c>
@@ -4322,13 +4780,17 @@
         <v>105</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+        <v>334</v>
+      </c>
+      <c r="F116">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
         <v>10</v>
       </c>
@@ -4339,13 +4801,17 @@
         <v>10</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E117" s="18" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+      <c r="F117">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="14" t="s">
         <v>10</v>
       </c>
@@ -4356,10 +4822,14 @@
         <v>10</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>343</v>
+        <v>338</v>
+      </c>
+      <c r="F118">
+        <f t="shared" si="1"/>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/service_group.xlsx
+++ b/service_group.xlsx
@@ -561,127 +561,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 독감 예방접종을 집에서 받을 수 있을까
-거동이 어려워 방문 예방접종이 필요하다
-폐렴 예방접종 상담이 필요하다
-어르신 예방접종을 병원 대신 집에서 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>상처 감염이 걱정되어 관리가 필요하다
-감염 예방 상담이 필요하다
-면역력이 약해 감염 관리가 필요하다
-상처 관리와 감염 예방이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>어르신 욕창이 있어서 집에서 치료가 필요하다
-상처 드레싱을 해야 하는데 병원 방문이 어렵다
-튜브 관리가 필요하다
-카테터 관리가 필요하다
-욕창 관리나 상처 치료를 집에서 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>어르신 건강 상태가 갑자기 나빠졌다
-호흡이 힘들어 응급 처치가 필요하다
-갑작스러운 증상이 있어 의료 도움이 필요하다
-집에서 응급 상황이 발생했다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>병원 방문이 어려워 집에서 의료 상담을 받고 싶다
-어르신 건강 문제로 방문진료 상담이 필요하다
-방문 의료 서비스에 대해 상담하고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>어르신 기본 간호가 필요하다
-병원 퇴원 후 간호 관리가 필요하다
-환자 상태를 관리해 줄 간호 서비스가 필요하다
-집에서 간호 서비스를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문 간호 상담이 필요하다
-간호 관련 서비스 문의
-어르신 간호 서비스 상담</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>재활 치료가 필요한지 평가받고 싶다
-뇌졸중 이후 재활 가능 여부를 확인하고 싶다
-신체 기능 상태를 평가받고 싶다
-재활 시작 전 평가가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>재활 운동 방법을 배우고 싶다
-재활 치료 상담이 필요하다
-어르신 재활 관리 방법 교육이 필요하다
-보호자가 재활 방법을 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>뇌졸중 이후 재활 운동이 필요하다
-관절염이 있어 재활 운동이 필요하다
-다리 힘이 약해 보행 훈련이 필요하다
-근력이 많이 약해져 운동 재활이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>손을 잘 사용하지 못해 작업치료가 필요하다
-일상생활 동작 훈련이 필요하다
-식사나 옷 입기 같은 생활 동작 훈련이 필요하다
-손 기능 재활이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>방문 재활 상담이 필요하다
-재활 치료 서비스 문의
-재활 관련 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>보건의료에 해당하는 기타 서비스</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>병원 방문이 어려워 전화 진료가 필요하다
-온라인으로 진료 상담을 받고 싶다
-비대면 진료 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>의료 차량이 와서 진료해 주는 서비스가 필요하다
-찾아오는 이동 진료가 필요하다
-지역 방문 의료 서비스가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>병원 퇴원 후 집에서 생활할 예정이라 의료 연계가 필요하다
-퇴원 환자 관리 서비스가 필요하다
-퇴원 이후 재가 의료 지원이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>말기 환자 돌봄 서비스가 필요하다
-임종 단계 환자 의료 지원이 필요하다
-호스피스나 임종 돌봄 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>구강 관리 전문 인력이 방문하여 대상자의 구강 건강 상태와 치아 상태를 평가하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 치아 상태가 안 좋아 보이는데 확인이 필요하다
-거동이 불편해서 치과를 가기 어렵다
-집에서 구강 상태를 점검받고 싶다
-어르신 치아 건강 상태를 확인하고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>구강 관리 전문 인력이 방문하여 구강 위생 관리 방법과 치아 관리에 대한 교육과 상담을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -690,34 +573,14 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 구강 관리 서비스 상담이 필요하다
-방문 구강 관리 서비스가 있는지 알고 싶다
-치아 관리 지원을 받을 수 있는지 궁금하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>약사가 방문하거나 상담을 통해 대상자의 약 복용 상태를 확인하고 복약 관리 필요성을 평가하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신이 약을 잘 챙겨 드시지 못한다
-여러 약을 먹고 있는데 관리가 필요하다
-복용 중인 약을 제대로 먹고 있는지 확인이 필요하다
-약을 빼먹거나 중복 복용하는 것 같다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>약 복용 방법과 약 관리 방법에 대해 대상자와 보호자에게 교육과 상담을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 약 먹는 방법을 알려주면 좋겠다
-약 복용 관리 상담이 필요하다
-약을 어떻게 먹어야 하는지 교육이 필요하다
-약 관리 방법을 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>방문복약관리 범주에 해당하는 기타 복약 관리 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -726,196 +589,78 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 건강 상태를 방문하여 복약체크 후 확인하고 싶다
-건강 관리가 필요한지 방문하여 복약으로 확인이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>어르신 건강 상태를 확인하고 싶다
-건강 관리가 필요한지 평가가 필요하다
-혼자 사는 어르신 건강 상태가 걱정된다
-어르신 건강 상태 점검이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신의 신체 기능 유지와 인지 기능 향상을 위한 운동 또는 인지 프로그램을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 운동 프로그램이 필요하다
-인지 기능 유지 프로그램이 필요하다
-어르신 활동 프로그램에 참여하고 싶다
-건강을 위한 운동 프로그램이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>대상자의 건강 관리에 필요한 지역사회 자원이나 서비스를 연계하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 건강 관리 지원을 받을 수 있는 연계가 필요하다.
-건강 관리 서비스를 어디서 받을 수 있는지 궁금하다
-지역 건강 관리 지원 서비스를 찾고 있다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>식습관, 운동, 생활 습관 개선을 위한 건강 교육과 상담을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 건강 생활 습관 상담이 필요하다
-식습관이나 운동 습관을 개선하고 싶다
-건강 관리 방법 교육이 필요하다
-생활 습관을 바꾸는 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>AI 또는 IoT 기기를 활용하여 대상자의 건강 상태를 원격으로 모니터링하고 관리하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 건강을 기기로 관리할 수 있는 서비스가 있나요
-집에서 건강 상태를 원격으로 관리하고 싶다
-스마트 기기로 건강 관리를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>건강관리 인력이 가정을 방문하여 대상자의 건강 상태를 확인하고 건강 관리 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 건강 상태를 집에서 관리받고 싶다
-방문 건강 관리 서비스를 받고 싶다
-혼자 사는 어르신 건강 관리가 걱정된다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>건강관리 범주에 해당하는 기타 건강 관리 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 건강 관리 서비스 상담이 필요하다
-건강 관리 지원을 받을 수 있는지 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>장애인의 기능 회복과 건강 유지를 위해 재활 서비스와 지원을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>장애가 있는 어르신 재활 서비스가 필요하다
-장애인 재활 지원을 받고 싶다
-장애로 인해 재활 치료가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>장애인의 건강 상태를 종합적으로 관리하고 필요한 건강 관리 서비스를 연계하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>장애인 건강 관리 지원이 필요하다
-장애가 있는 어르신 건강 관리가 필요하다
-장애인 통합 건강 관리 서비스를 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>장애인이 이용하기 편리한 환경에서 건강검진을 받을 수 있도록 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>장애인이 받을 수 있는 건강검진이 있나요
-장애인 건강검진 지원이 필요하다
-장애 친화 건강검진 서비스를 찾고 있다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>장애 여성을 대상으로 이용 편의를 고려한 산부인과 진료 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>장애 여성을 위한 산부인과 서비스가 있나요
-장애인 산부인과 진료 지원이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>장애인 건강관리 범주에 해당하는 기타 건강 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>장애인 건강 관리 서비스 상담이 필요하다
-장애인 건강 지원을 받을 수 있는지 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>치매 여부를 조기에 확인하기 위해 인지 기능 검사를 실시하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 기억력이 많이 떨어진 것 같다
-치매 검사를 받아보고 싶다
-어르신 치매 초기 검사가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>치매 환자의 인지 기능 유지와 돌봄 지원을 위해 쉼터 프로그램을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 어르신 낮 동안 돌봄이 필요하다
-치매 환자가 이용할 수 있는 쉼터가 있나요
-치매 환자 프로그램이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>치매 환자를 돌보는 가족을 위한 교육과 상담, 지원 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 환자를 돌보는 가족이 너무 힘들다
-치매 가족 지원 서비스를 알고 싶다
-치매 환자 보호자 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>치매 환자의 일상 생활을 돕기 위한 돌봄 물품을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 어르신 돌봄 물품 지원이 있나요
-치매 환자 기저귀 같은 지원이 필요한데
-치매 돌봄 물품을 받을 수 있는지 궁금하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>치매 환자를 대상으로 전화 또는 온라인을 통한 비대면 진료 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 환자 비대면 진료가 가능한가요
-치매 환자 온라인 진료 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>치매 환자를 대상으로 의료진이 가정을 방문하여 진료를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 어르신 방문 진료가 필요하다
-치매 환자를 집에서 진료받고 싶다
-치매 환자가 병원 가기 어려워 방문 진료가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>치매 환자의 상태를 지속적으로 관리하고 필요한 서비스와 자원을 연계하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 환자 관리 상담이 필요하다
-치매 환자 돌봄 서비스를 연계받고 싶다
-치매 환자 사례 관리 지원이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>정신건강 위기 상황에 있는 대상자에게 긴급 상담과 지원을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -924,273 +669,110 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매환자를 위한 서비스가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>우울, 불안 등 정신건강 문제를 가진 대상자에게 상담과 지속적인 사례 관리를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신이 우울해 보인다
-정신 건강 상담이 필요하다
-우울증 상담을 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>정신질환 예방과 회복을 위해 상담과 재활 프로그램을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>정신 건강 회복 프로그램이 필요하다
-정신질환 예방을 위한 서비스가 필요하다
-정신 건강 재활 프로그램이 있나요</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>어르신 정신 상태가 많이 불안하다
-위기 상담이 필요하다
-정신적으로 힘들어 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>정신건강 관리 방법과 관련 정보에 대한 교육과 안내를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>정신 건강 관리 방법을 알고 싶다
-정신 건강 관련 교육이 필요하다
-우울 예방 방법을 배우고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>정신건강관리 범주에 해당하는 기타 정신 건강 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>정신 건강 상담 서비스를 알고 싶다
-정신 건강 관련 도움을 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>건강관리 예방 관련 기타 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>건강관리에 대한 상담서비스나 관련 도움을 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>요양보호사가 가정을 방문하여 어르신의 식사, 이동, 배변, 목욕 등 일상적인 신체 활동을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>혼자 생활이 어려운 어르신 돌봄이 필요하다
-식사나 이동을 도와줄 사람이 필요하다
-몸이 불편한 어르신 일상생활 도움이 필요하다
-어르신 집에서 돌봄 서비스를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>요양보호사가 방문하여 치매 예방 및 인지 기능 유지 활동을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 기억력이 많이 떨어진 것 같다
-인지 활동 프로그램이 필요하다
-치매 예방 활동을 지원받고 싶다
-어르신 두뇌 활동 프로그램이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>인지 기능이 저하된 어르신을 대상으로 인지 상태 관리와 생활 지원을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 초기 어르신 관리가 필요하다
-기억력이 많이 떨어진 어르신 돌봄이 필요하다
-인지 기능이 저하된 어르신 관리가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>요양보호사가 방문하여 어르신의 정서 안정과 사회적 교류를 위한 지원을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>혼자 사는 어르신이 많이 외로워한다
-어르신 정서 지원이 필요하다
-말벗이나 정서 돌봄이 필요하다
-어르신 우울감이 있는 것 같다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>요양보호사가 방문하여 청소, 세탁, 식사 준비 등 일상생활과 가사 활동을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 집안일을 도와줄 사람이 필요하다
-청소나 식사 준비를 도와줄 서비스가 필요하다
-혼자 사는 어르신 가사 지원이 필요하다
-일상생활 지원을 받을 수 있는지 궁금하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>간호사가 방문하여 어르신의 건강 상태를 확인하고 건강 관리 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 건강 상태가 걱정된다
-집에서 건강 관리를 받고 싶다
-혈압이나 혈당 관리를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>간호사가 방문하여 상처 관리, 의료 처치 등 필요한 간호 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>집에서 간호 처치가 필요하다
-상처 관리나 간호 지원이 필요하다
-간호사가 방문해서 관리해주면 좋겠다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>목욕 차량을 이용하여 이동식 목욕 시설에서 어르신에게 목욕 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 목욕을 시켜드리기 어렵다
-방문 목욕 서비스를 받고 싶다
-목욕 차량 서비스가 있는지 궁금하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>요양보호사가 가정을 방문하여 어르신의 목욕을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>집에서 목욕을 도와줄 서비스가 필요하다
-어르신 목욕을 시켜드리기 힘들다
-거동이 불편해 목욕 지원이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신이 낮 동안 보호시설에서 생활하며 신체 활동 지원을 받는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>낮 동안 어르신을 맡길 곳이 필요하다
-주야간보호센터 이용이 가능한지 궁금하다
-어르신 낮 돌봄 서비스가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>주야간 보호시설에서 인지 활동과 의사소통 지원 프로그램을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 어르신 낮 돌봄 서비스가 필요하다
-인지 프로그램이 있는 돌봄 시설이 필요하다
-어르신 인지 활동 프로그램이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>주야간 보호시설에서 어르신의 건강 상태 확인과 간호 관리를 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>건강 관리를 해주는 돌봄 시설이 필요하다
-간호 관리가 가능한 주야간 보호센터가 있나요
-어르신 건강 관리 돌봄 서비스가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>주야간 보호시설에서 어르신의 신체 기능 유지와 회복을 위한 운동 프로그램을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 재활 운동 프로그램이 필요하다
-기능 회복 운동을 할 수 있는 곳이 필요하다
-재활 활동 프로그램이 있는 시설이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신이 일정 기간 보호시설에 머물며 신체 활동 지원을 받는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>며칠 동안 어르신을 맡길 곳이 필요하다
-단기 보호 서비스를 이용하고 싶다
-잠시 어르신 돌봄이 필요한 상황이다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>단기 보호시설에서 인지 활동과 의사소통 지원을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치매 어르신 단기 보호가 필요하다
-인지 활동 프로그램이 있는 보호시설이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>단기 보호시설에서 어르신의 건강 관리와 간호 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>건강 관리가 가능한 단기 보호 시설이 필요하다
-간호 관리가 가능한 보호시설을 찾고 있다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>단기 보호시설에서 재활 운동과 기능 회복 프로그램을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>재활 프로그램이 있는 단기 보호 시설이 필요하다
-어르신 기능 회복 운동을 할 수 있는 시설이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신의 생활 편의를 위해 필요한 복지용구를 대여하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 휠체어나 보행기를 빌리고 싶다
-복지용구 대여 서비스가 있는지 궁금하다
-어르신 생활 보조 기구가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신의 생활을 돕기 위한 복지용구를 구입 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 복지용구를 구입하고 싶다
-보행기나 안전 손잡이를 설치하고 싶다
-생활 보조 기구 구입 지원이 있나요</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>방문요양, 방문목욕, 방문간호 등 다양한 재가 서비스를 통합적으로 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 집에서 여러 돌봄 서비스를 함께 받고 싶다
-통합 돌봄 서비스가 가능한지 궁금하다
-집에서 종합적인 돌봄 지원이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>요양 범주에 해당하는 기타 돌봄 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 돌봄 서비스 상담이 필요하다
-요양 서비스를 받을 수 있는지 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>일상생활돌봄 서비스로 돌봄 인력이 가정을 방문하여 어르신의 세면, 목욕 등 개인 위생 관리를 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1199,255 +781,103 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 옷 갈아입는 것을 도와줄 사람이 필요하다
-거동이 불편해 옷 입고 벗기가 어렵다
-몸이 불편한 어르신 생활 활동 도움이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>일상생활돌봄 서비스로 돌봄 인력이 가정을 방문하여 어르신이 집안에서 안전하게 이동할 수 있도록 보행과 이동을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신이 집안에서 이동하기 어렵다
-거동이 불편해 집안 이동 도움이 필요하다
-어르신 보행을 도와줄 사람이 필요하다
-집안에서 넘어질까 걱정된다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>일상생활돌봄 서비스로 돌봄 인력이 어르신의 화장실 이용을 안전하게 돕는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 화장실 이용을 도와줄 사람이 필요하다
-거동이 불편해 화장실 이용이 어렵다
-어르신 배변 활동 도움을 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>일상생활돌봄 서비스로 돌봄 인력이 어르신의 식사 활동을 돕고 식사 지원을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 식사를 챙겨드리기 어렵다
-식사를 혼자 하기 힘든 어르신 도움이 필요하다
-어르신 식사 지원 서비스가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>일상생활지원 범주에 해당하는 기타 생활 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 일상생활 지원 상담이 필요하다
-생활 돌봄 서비스를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>돌봄 인력이 방문하여 어르신의 주거 공간 청소 등 가사 활동을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 집 청소를 도와줄 사람이 필요하다
-혼자 사는 어르신 집안 정리가 어렵다
-청소 지원 서비스를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>돌봄 인력이 방문하여 어르신의 세탁과 빨래 활동을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 빨래를 하기 어렵다
-세탁을 도와줄 사람이 필요하다
-빨래 지원 서비스를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>돌봄 인력이 방문하여 어르신의 식사 준비와 간단한 조리를 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 식사 준비가 어렵다
-밥을 해 드리기 어려운 상황이다
-식사 준비 지원이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>가사지원 범주에 해당하는 기타 가사 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 가사 지원 상담이 필요하다
-집안일 도움을 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>돌봄 인력이 어르신의 병원 방문이나 외출 시 동행하여 이동을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 병원 갈 때 동행이 필요하다
-외출할 때 도와줄 사람이 필요하다
-어르신 병원 동행 서비스가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신의 이동을 위해 차량을 이용한 이동 지원 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 병원 갈 때 차량 지원이 필요하다
-이동 차량 서비스를 이용하고 싶다
-어르신 이동 지원 차량이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>이동지원 범주에 해당하는 기타 이동 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 이동 지원 상담이 필요하다
-외출 이동 서비스를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신에게 식사를 제공하기 위해 도시락 배달 서비스를 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>혼자 사는 어르신 식사 배달이 필요하다
-도시락 지원 서비스를 받고 싶다
-어르신 식사 배달 서비스가 있나요</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>어르신의 식사를 위해 필요한 식재료 구입을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 장보기가 어렵다
-식재료 구입 도움을 받고 싶다
-어르신 장보기 지원이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>식사지원 범주에 해당하는 기타 식사 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 식사 지원 상담이 필요하다
-식사 돌봄 서비스를 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>이미용 인력이 방문하여 어르신의 머리 손질, 이발, 미용 서비스를 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 머리를 집에서 잘라주면 좋겠다
-거동이 불편해 미용실 가기 어렵다
-방문 이미용 서비스를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>청력이 저하된 어르신을 위해 보청기 사용과 관련된 지원을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 귀가 잘 안 들린다
-보청기 지원을 받을 수 있는지 궁금하다
-청력 문제로 의사소통이 어렵다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>청각 장애인이 의사소통을 할 수 있도록 수화 통역을 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>수화 통역 지원이 필요하다
-청각 장애인 의사소통 지원이 필요하다
-수화 통역 서비스를 이용하고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>의사소통지원 범주에 해당하는 기타 의사소통 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>의사소통 지원 상담이 필요하다
-소통 지원 서비스를 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>스마트 기기 또는 돌봄 인력을 통해 어르신의 안부와 안전 상태를 확인하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>혼자 사는 어르신 안부 확인이 필요하다
-어르신 안전이 걱정된다
-어르신 상태를 확인해주는 서비스가 있나요</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>스마트 기술이나 돌봄 서비스를 통해 어르신의 정서 안정과 사회적 교류를 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신이 많이 외로워한다
-정서 지원 서비스가 필요하다
-어르신 말벗 서비스가 있나요</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>스마트돌봄 범주에 해당하는 기타 스마트 돌봄 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>스마트 돌봄 서비스 상담이 필요하다
-어르신 안전 관리 서비스를 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>스마트돌봄 범주에 해당하는 기타 스마트 돌봄 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>스마트 돌봄 서비스 상담이 필요하다
-어르신 안전 관리 서비스를 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>주거복지 서비스로 어르신이나 거동이 불편한 대상자가 안전하게 생활할 수 있도록 문턱 제거, 안전손잡이 설치 등 주거 환경을 개선하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 집에 문턱이 높아 넘어질까 걱정된다
-집에 안전 손잡이를 설치하고 싶다
-거동이 불편한 어르신 주거 환경 개선이 필요하다
-어르신 낙상 예방을 위한 집 구조 개선이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>주거복지 서비스로 전등 교체, 간단한 집수리 등 기본적인 주거 환경 보수를 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 집 전등이 고장났는데 수리가 어렵다
-혼자 사는 어르신 집수리가 필요하다
-집안 간단한 수리를 도와줄 서비스가 있나요
-어르신 주거 환경 보수가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>주거복지 서비스로 어르신 가정을 방문하여 방역과 소독을 지원하는 서비스</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>어르신 집 방역이 필요하다
-집안 위생 관리가 필요하다
-혼자 사는 어르신 집 소독을 하고 싶다</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -1460,144 +890,62 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>퇴원 후 바로 집에 가기 어려운 상황이다
-어르신이 잠시 머물 수 있는 시설이 필요하다
-퇴원 후 적응을 위한 거주 지원이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>돌봄이 필요한 대상자가 안전하게 장기간 거주할 수 있도록 지원하는 주거 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>돌봄이 가능한 주택이 필요하다
-어르신이 장기간 거주할 수 있는 돌봄 주택이 있나요
-케어안심주택 지원을 받고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>주거지원 범주에 해당하는 기타 주거 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 주거 지원 상담이 필요하다
-돌봄 가능한 주거 서비스를 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>주거복지 범주에 해당하는 기타 주거 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 주거 복지 상담이 필요하다
-주거 관련 지원 서비스를 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>농업 활동을 활용하여 돌봄, 재활, 정서 지원 등을 제공하는 케어팜 프로그램 운영 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 농업 체험 프로그램이 필요하다
-돌봄과 농업 활동을 함께 하는 프로그램이 있나요
-케어팜 프로그램에 참여하고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>농업 돌봄 연계 범주에 해당하는 기타 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>농업 돌봄 프로그램 상담이 필요하다
-케어팜 관련 서비스를 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>지역 경로당 등에서 어르신의 건강 관리와 돌봄 프로그램을 운영하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 건강 프로그램에 참여하고 싶다
-경로당 건강 돌봄 프로그램이 있나요
-어르신 돌봄 교실이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>건강돌봄 통합지원 범주에 해당하는 기타 건강 돌봄 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>건강 돌봄 프로그램 상담이 필요하다
-지역 돌봄 프로그램을 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>지역 주민이 돌봄 활동에 참여할 수 있도록 돌봄 매니저 또는 활동가를 양성하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>돌봄 활동가로 참여하고 싶다
-돌봄 매니저 교육이 있나요
-지역 돌봄 활동에 참여하고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>지역 주민이 건강 관리 활동을 주도할 수 있도록 건강 리더를 양성하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>지역 건강 활동에 참여하고 싶다
-건강 리더 교육 프로그램이 있나요
-건강 관리 활동가가 되고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>돌봄특화 주민참여 범주에 해당하는 기타 주민 참여 돌봄 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>지역 돌봄 활동 상담이 필요하다
-주민 참여 돌봄 프로그램을 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>돌봄이 필요한 대상자가 전화 등을 통해 돌봄 서비스를 요청하거나 상담 받을 수 있도록 지원하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>돌봄 상담 전화를 하고 싶다
-어르신 돌봄 서비스를 문의하고 싶다
-돌봄 지원 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>돌봄이 필요한 대상자를 위해 24시간 상시 돌봄 지원을 제공하는 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>어르신 24시간 돌봄이 필요하다
-밤에도 돌봄 지원을 받을 수 있나요
-긴급 돌봄 서비스가 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>상시돌봄지원 범주에 해당하는 기타 돌봄 지원 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>상시 돌봄 서비스 상담이 필요하다
-돌봄 지원 서비스를 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>기타 통합돌봄 서비스</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>위 내용에 포함하지 않은 통합돌봄  서비스를 알고싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>의료처치(욕창, 루, 튜브관리 등)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1606,38 +954,379 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>질병 관리 방법을 의사에게 상담받고 싶다
-어르신 건강 관리 방법에 대해 상담이 필요하다
-병원 방문이 어려워 집에서 상담을 받고 싶다
-보호자가 질환 관리 방법을 알고 싶다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>먹는 약이 너무 많아 상담이 필요하다
-거동이 불편해  집에서 약 처방을 받고 싶다
-현재 복용 중인 약이 맞는지 의사가 확인해주면 좋겠다
-고령이라 약을 줄이는 탈처방 상담이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>당뇨가, 고혈압이 있어 정기적으로 건강 상태 확인이 필요하다
-만성질환이 있어 방문 간호 건강 관리가 필요하다
-어르신 건강 상태를 정기적으로 체크해 줄 사람이 필요하다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>어르신 목욕을 혼자 하기 어렵다
-거동이 불편해 세수나 목욕을 도와줄 사람이 필요하다
-거동이 불편한 어르신 위생 관리 지원이 필요하다
-어르신 목욕을 시켜드리기 어려운 상황이다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>건강 상태 전반을 평가받고 싶다
-질환으로 방문진료를 활용한 건강 상태를 확인하고 싶다
-건강 상태의 종합적 확인 및 돌봄 계획을 세우고 싶다
-집에서 의사가 건강을 평가해주면 좋겠다</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>방문진료로 건강 상태 종합 평가 및 확인, 집에서 의사 진료와 돌봄 계획 수립 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>질병·건강 관리 방법 의사 상담 희망, 병원 방문 어려워 집에서 상담 필요, 보호자도 관리 방법 상담 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>복약 많아 상담 필요, 거동 불편으로 방문 처방 희망, 복약 적정성 확인 및 탈처방 상담 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>독감·폐렴 예방접종 상담 및 방문 접종 희망, 거동 어려워 병원 대신 집에서 접종 원함</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>욕창·상처 드레싱 및 튜브·카테터 관리 필요, 병원 방문 어려워 집에서 치료 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상처 감염 우려로 관리 및 예방 상담 필요, 면역력 저하로 감염 관리 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강 급악화 및 호흡곤란 등 응급상황 발생, 집에서 즉시 의료 처치 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원 방문 어려워 집에서 의료·방문진료 상담 희망, 방문 의료 서비스 상담 원함</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>당뇨·고혈압 등 만성질환으로 정기 건강 확인 필요, 방문간호 등 지속 관리 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 간호 및 퇴원 후 상태 관리 필요, 집에서 간호 서비스 이용 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문간호 포함 간호 서비스 상담 및 문의 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>뇌졸중 이후 재활 가능 여부 및 신체 기능 평가, 재활 시작 전 평가 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>재활 운동·치료 상담 및 관리 방법 교육 희망, 보호자도 재활 방법 교육 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>뇌졸중·관절염 등으로 재활 운동 및 보행 훈련 필요, 근력 저하로 운동 재활 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>손 기능 저하로 작업치료 및 일상생활 동작(식사·옷입기) 훈련 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문재활 포함 재활 치료 서비스 상담 및 문의 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>보건의료에 해당하는 기타 서비스</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>병원 방문 어려워 전화·온라인 등 비대면 진료 상담 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>의료 차량 방문 진료 및 이동형 의료 서비스 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>퇴원 후 재가 생활 위해 의료 연계 및 환자 관리·재가 의료 지원 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>말기·임종 단계 환자 돌봄 및 의료 지원 필요, 호스피스 상담 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>치아 상태 확인 필요, 거동 불편으로 치과 방문 어려워 집에서 구강 상태 점검 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문 구강 관리 포함 치아 관리 서비스 상담 및 이용 가능 여부 문의</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>복약 관리 필요, 약 복용 누락·중복 우려로 복용 상태 확인 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>약 복용 방법 교육 및 관리 상담 희망, 약 관리 방법 안내 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>방문하여 복약 체크 후 건강 상태 확인 및 관리 필요 여부 평가 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>어르신 건강 상태 점검 및 관리 필요 여부 평가 희망, 독거로 건강 상태 우려</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>어르신 운동·인지 기능 유지 프로그램 필요 및 참여 희망</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강 관리 지원 연계 및 지역 서비스 이용 가능 기관 안내 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>건강 생활습관 상담 및 식사·운동 습관 개선 교육 필요</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>어르신 건강을 기기로 관리 희망, 집에서 원격 건강 관리 및 스마트 기기 활용 건강 관리 희망</t>
+  </si>
+  <si>
+    <t>어르신 건강 상태 집에서 관리 희망, 방문 건강 관리 서비스 이용 필요, 독거로 건강 관리 우려</t>
+  </si>
+  <si>
+    <t>어르신 건강 관리 서비스 상담 및 지원 가능 여부 확인 희망</t>
+  </si>
+  <si>
+    <t>장애로 재활 치료 필요, 장애 어르신 재활 서비스 및 재활 지원 이용 희망</t>
+  </si>
+  <si>
+    <t>장애 어르신 건강 관리 필요, 장애인 통합 건강 관리 지원 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>장애인 건강검진 필요, 장애 친화 건강검진 지원 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>장애 여성 산부인과 진료 필요, 관련 의료 서비스 지원 희망</t>
+  </si>
+  <si>
+    <t>장애인 건강 관리 서비스 상담 및 지원 가능 여부 확인 희망</t>
+  </si>
+  <si>
+    <t>어르신 기억력 저하로 치매 검사 및 초기 진단 필요</t>
+  </si>
+  <si>
+    <t>치매 어르신 낮 돌봄 필요, 쉼터 및 치매 프로그램 이용 희망</t>
+  </si>
+  <si>
+    <t>치매 가족 돌봄 부담으로 가족 지원 서비스 및 보호자 상담 필요</t>
+  </si>
+  <si>
+    <t>치매 돌봄 물품 지원 필요, 기저귀 등 지원 가능 여부 확인 희망</t>
+  </si>
+  <si>
+    <t>치매 환자 비대면 진료 가능 여부 문의 및 온라인 진료 상담 필요</t>
+  </si>
+  <si>
+    <t>치매 환자 병원 방문 어려워 집에서 방문 진료 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>치매 환자 관리 상담 필요, 돌봄 서비스 연계 및 사례관리 지원 희망</t>
+  </si>
+  <si>
+    <t>치매 환자를 위한 돌봄 및 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>어르신 우울감 및 정신 건강 문제로 상담 및 우울증 상담 희망</t>
+  </si>
+  <si>
+    <t>정신 건강 회복 및 예방 위한 프로그램 및 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>어르신 정신 상태 불안으로 위기 상담 및 정신 건강 상담 필요</t>
+  </si>
+  <si>
+    <t>정신 건강 관리 방법 및 우울 예방 교육 상담 필요</t>
+  </si>
+  <si>
+    <t>정신 건강 상담 서비스 이용 및 관련 지원 필요</t>
+  </si>
+  <si>
+    <t>건강 관리 상담 서비스 및 관련 지원 이용 희망</t>
+  </si>
+  <si>
+    <t>혼자 생활 어려워 식사·이동 등 일상생활 돌봄 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>인지 기능 저하로 인지 활동 및 치매 예방 프로그램 이용 필요</t>
+  </si>
+  <si>
+    <t>치매 초기 및 인지 저하 어르신 관리 및 돌봄 서비스 필요</t>
+  </si>
+  <si>
+    <t>어르신 외로움 및 우울감 있어 말벗 등 정서 지원 서비스 필요</t>
+  </si>
+  <si>
+    <t>혼자 생활 어려워 청소·식사 준비 등 가사 지원 서비스 필요</t>
+  </si>
+  <si>
+    <t>어르신 건강 상태 우려로 혈압·혈당 등 건강 관리 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>상처 관리 등 간호 처치 필요하여 간호사 방문 간호 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>어르신 목욕 어려워 방문 목욕 서비스 및 목욕 차량 이용 희망</t>
+  </si>
+  <si>
+    <t>거동 불편으로 집에서 목욕 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>낮 동안 돌봄 필요, 주야간 보호센터 및 낮 돌봄 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>치매 어르신 낮 돌봄 필요, 인지 프로그램 제공 시설 이용 희망</t>
+  </si>
+  <si>
+    <t>건강 관리 가능한 주야간 보호시설 및 돌봄 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>어르신 재활 운동 및 기능 회복 위한 프로그램 이용 필요</t>
+  </si>
+  <si>
+    <t>단기간 어르신 돌봄 필요, 단기 보호 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>치매 어르신 단기 보호 및 인지 프로그램 제공 시설 이용 필요</t>
+  </si>
+  <si>
+    <t>건강 관리 가능한 단기 보호시설 및 간호 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>재활 프로그램 가능한 단기 보호시설 및 기능 회복 서비스 필요</t>
+  </si>
+  <si>
+    <t>어르신 보행기 등 복지용구 대여 및 생활 보조 기구 이용 희망</t>
+  </si>
+  <si>
+    <t>복지용구 구입 희망, 보행기·안전손잡이 등 설치 및 지원 필요</t>
+  </si>
+  <si>
+    <t>어르신 집에서 통합 돌봄 서비스 및 종합적 지원 이용 희망</t>
+  </si>
+  <si>
+    <t>어르신 돌봄 서비스 상담 및 요양 서비스 이용 가능 여부 확인 희망</t>
+  </si>
+  <si>
+    <t>거동 불편으로 위생 관리 어려워 목욕 등 위생 지원 서비스 필요</t>
+  </si>
+  <si>
+    <t>거동 불편으로 옷 입고 벗기 어려워 생활 활동 지원 필요</t>
+  </si>
+  <si>
+    <t>거동 불편으로 집안 이동 어려워 이동 및 보행 지원 필요</t>
+  </si>
+  <si>
+    <t>거동 불편으로 화장실 이용 어려워 배변 활동 지원 필요</t>
+  </si>
+  <si>
+    <t>어르신 식사 어려워 식사 지원 및 돌봄 서비스 필요</t>
+  </si>
+  <si>
+    <t>혼자 생활 어려워 집 청소 등 청소 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>세탁 어려워 빨래 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>식사 준비 어려워 식사 준비 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>가사 지원 상담 및 집안일 도움 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>병원 방문 시 보호자 없어 병원 동행 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>병원 이동 어려워 차량 이동 지원 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>외출 및 이동 지원 서비스 상담 및 이용 희망</t>
+  </si>
+  <si>
+    <t>혼자 생활 어려워 식사 배달 및 도시락 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>장보기 어려워 식재료 구입 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>식사 지원 서비스 상담 및 돌봄 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>거동 불편으로 미용실 방문 어려워 방문 이미용 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>청력 저하로 보청기 지원 및 의사소통 개선 서비스 필요</t>
+  </si>
+  <si>
+    <t>청각 장애로 수화 통역 등 의사소통 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>의사소통 지원 서비스 상담 및 관련 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>독거 어르신 안전 확인 필요, 안부 확인 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>어르신 외로움 해소 위해 정서 지원 및 말벗 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>스마트 돌봄 서비스 상담 및 어르신 안전 관리 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>어르신 주거 환경 위험으로 손잡이 설치 등 낙상 예방 환경 개선 필요</t>
+  </si>
+  <si>
+    <t>집 수리 어려워 주거 환경 보수 및 집수리 지원 서비스 이용 필요</t>
+  </si>
+  <si>
+    <t>집 위생 문제로 방역 및 소독 등 환경 관리 서비스 필요</t>
+  </si>
+  <si>
+    <t>주거 환경 개선 상담 및 구조 개선 지원 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>퇴원 후 집 복귀 어려워 임시 거주 및 재가 적응 지원 필요</t>
+  </si>
+  <si>
+    <t>돌봄 가능한 주택 필요, 케어안심주택 등 장기 거주 지원 희망</t>
+  </si>
+  <si>
+    <t>어르신 주거 지원 상담 및 돌봄 가능한 주거 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>주거 복지 상담 및 주거 관련 지원 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>농업 활동 통한 돌봄 프로그램 필요, 케어팜 참여 희망</t>
+  </si>
+  <si>
+    <t>농업 돌봄 프로그램 상담 및 케어팜 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>건강 프로그램 참여 희망, 경로당 등 건강 돌봄 프로그램 이용 필요</t>
+  </si>
+  <si>
+    <t>지역 건강 돌봄 프로그램 상담 및 참여 희망</t>
+  </si>
+  <si>
+    <t>돌봄 활동 참여 희망, 돌봄 매니저 교육 및 지역 활동 참여 필요</t>
+  </si>
+  <si>
+    <t>건강 활동 참여 희망, 건강 리더 교육 및 활동 프로그램 이용 필요</t>
+  </si>
+  <si>
+    <t>지역 돌봄 활동 상담 및 주민 참여 프로그램 이용 희망</t>
+  </si>
+  <si>
+    <t>돌봄 서비스 문의 및 상담 전화 이용 필요</t>
+  </si>
+  <si>
+    <t>24시간 돌봄 필요, 야간 포함 긴급 돌봄 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>상시 돌봄 서비스 상담 및 돌봄 지원 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>기타 통합돌봄 서비스 및 추가 지원 서비스 정보 이용 희망</t>
+  </si>
+  <si>
+    <t>일상생활 지원 서비스 상담 및 생활 돌봄 서비스 이용 희망</t>
   </si>
 </sst>
 </file>
@@ -2352,6 +2041,7 @@
     <col min="3" max="3" width="39.625" style="3" customWidth="1"/>
     <col min="4" max="4" width="102.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="100.625" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2374,7 +2064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -2388,14 +2078,14 @@
         <v>112</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>345</v>
+        <v>231</v>
       </c>
       <c r="F2">
         <f>LEN(E2)</f>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2409,14 +2099,14 @@
         <v>113</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>341</v>
+        <v>232</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F66" si="0">LEN(E3)</f>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -2430,14 +2120,14 @@
         <v>114</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>342</v>
+        <v>233</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>2</v>
       </c>
@@ -2451,14 +2141,14 @@
         <v>115</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>133</v>
+        <v>234</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="82.5" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>2</v>
       </c>
@@ -2466,20 +2156,20 @@
         <v>3</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>339</v>
+        <v>229</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>116</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>135</v>
+        <v>235</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>2</v>
       </c>
@@ -2493,14 +2183,14 @@
         <v>117</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>134</v>
+        <v>236</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>2</v>
       </c>
@@ -2514,14 +2204,14 @@
         <v>118</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>2</v>
       </c>
@@ -2535,15 +2225,15 @@
         <v>119</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>2</v>
       </c>
@@ -2557,14 +2247,14 @@
         <v>120</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>343</v>
+        <v>239</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>2</v>
       </c>
@@ -2578,14 +2268,14 @@
         <v>121</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>138</v>
+        <v>240</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="49.5" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>2</v>
       </c>
@@ -2599,14 +2289,14 @@
         <v>122</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>2</v>
       </c>
@@ -2620,14 +2310,14 @@
         <v>123</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>140</v>
+        <v>242</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>2</v>
       </c>
@@ -2641,14 +2331,14 @@
         <v>124</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>2</v>
       </c>
@@ -2662,14 +2352,14 @@
         <v>125</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>142</v>
+        <v>244</v>
       </c>
       <c r="F15">
         <f t="shared" si="0"/>
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>2</v>
       </c>
@@ -2683,14 +2373,14 @@
         <v>126</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>143</v>
+        <v>245</v>
       </c>
       <c r="F16">
         <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>2</v>
       </c>
@@ -2704,11 +2394,11 @@
         <v>127</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>144</v>
+        <v>246</v>
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2725,14 +2415,14 @@
         <v>128</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>145</v>
+        <v>247</v>
       </c>
       <c r="F18">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>2</v>
       </c>
@@ -2746,14 +2436,14 @@
         <v>129</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>146</v>
+        <v>248</v>
       </c>
       <c r="F19">
         <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
         <v>2</v>
       </c>
@@ -2767,14 +2457,14 @@
         <v>130</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>147</v>
+        <v>249</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>2</v>
       </c>
@@ -2788,14 +2478,14 @@
         <v>131</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>148</v>
+        <v>250</v>
       </c>
       <c r="F21">
         <f t="shared" si="0"/>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
         <v>2</v>
       </c>
@@ -2809,14 +2499,14 @@
         <v>132</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>149</v>
+        <v>251</v>
       </c>
       <c r="F22">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>23</v>
       </c>
@@ -2827,14 +2517,14 @@
         <v>15</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="F23">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2848,17 +2538,17 @@
         <v>5</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="F24">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
@@ -2869,17 +2559,17 @@
         <v>10</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>154</v>
+        <v>253</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>23</v>
       </c>
@@ -2890,17 +2580,17 @@
         <v>15</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="F26">
         <f t="shared" si="0"/>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>23</v>
       </c>
@@ -2911,17 +2601,17 @@
         <v>5</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>158</v>
+        <v>255</v>
       </c>
       <c r="F27">
         <f t="shared" si="0"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
         <v>23</v>
       </c>
@@ -2932,17 +2622,17 @@
         <v>10</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="F28">
         <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>23</v>
       </c>
@@ -2953,17 +2643,17 @@
         <v>15</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="F29">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
         <v>23</v>
       </c>
@@ -2974,17 +2664,17 @@
         <v>24</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="F30">
         <f t="shared" si="0"/>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>23</v>
       </c>
@@ -2995,17 +2685,17 @@
         <v>25</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>166</v>
+        <v>259</v>
       </c>
       <c r="F31">
         <f t="shared" si="0"/>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
         <v>23</v>
       </c>
@@ -3016,17 +2706,17 @@
         <v>26</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>168</v>
+        <v>260</v>
       </c>
       <c r="F32">
         <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>23</v>
       </c>
@@ -3037,17 +2727,17 @@
         <v>27</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>170</v>
+        <v>261</v>
       </c>
       <c r="F33">
         <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
         <v>23</v>
       </c>
@@ -3055,20 +2745,20 @@
         <v>12</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>340</v>
+        <v>230</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>172</v>
+        <v>262</v>
       </c>
       <c r="F34">
         <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>23</v>
       </c>
@@ -3079,17 +2769,17 @@
         <v>10</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>174</v>
+        <v>263</v>
       </c>
       <c r="F35">
         <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
         <v>23</v>
       </c>
@@ -3100,17 +2790,17 @@
         <v>29</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="F36">
         <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>23</v>
       </c>
@@ -3121,17 +2811,17 @@
         <v>30</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>178</v>
+        <v>265</v>
       </c>
       <c r="F37">
         <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
         <v>23</v>
       </c>
@@ -3142,17 +2832,17 @@
         <v>31</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>180</v>
+        <v>266</v>
       </c>
       <c r="F38">
         <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>23</v>
       </c>
@@ -3163,17 +2853,17 @@
         <v>32</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>182</v>
+        <v>267</v>
       </c>
       <c r="F39">
         <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>23</v>
       </c>
@@ -3184,17 +2874,17 @@
         <v>10</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>184</v>
+        <v>268</v>
       </c>
       <c r="F40">
         <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>23</v>
       </c>
@@ -3205,17 +2895,17 @@
         <v>34</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>186</v>
+        <v>269</v>
       </c>
       <c r="F41">
         <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>23</v>
       </c>
@@ -3226,17 +2916,17 @@
         <v>35</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="F42">
         <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
         <v>23</v>
       </c>
@@ -3247,17 +2937,17 @@
         <v>36</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>190</v>
+        <v>271</v>
       </c>
       <c r="F43">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>23</v>
       </c>
@@ -3268,17 +2958,17 @@
         <v>37</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="F44">
         <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>23</v>
       </c>
@@ -3289,17 +2979,17 @@
         <v>38</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>194</v>
+        <v>273</v>
       </c>
       <c r="F45">
         <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
         <v>23</v>
       </c>
@@ -3310,17 +3000,17 @@
         <v>39</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>196</v>
+        <v>274</v>
       </c>
       <c r="F46">
         <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>23</v>
       </c>
@@ -3331,14 +3021,14 @@
         <v>40</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>198</v>
+        <v>275</v>
       </c>
       <c r="F47">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -3352,17 +3042,17 @@
         <v>10</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>201</v>
+        <v>276</v>
       </c>
       <c r="F48">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>23</v>
       </c>
@@ -3373,17 +3063,17 @@
         <v>42</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>203</v>
+        <v>277</v>
       </c>
       <c r="F49">
         <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>23</v>
       </c>
@@ -3394,17 +3084,17 @@
         <v>43</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>205</v>
+        <v>278</v>
       </c>
       <c r="F50">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>23</v>
       </c>
@@ -3415,17 +3105,17 @@
         <v>44</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>206</v>
+        <v>279</v>
       </c>
       <c r="F51">
         <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>23</v>
       </c>
@@ -3436,17 +3126,17 @@
         <v>45</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="F52">
         <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>23</v>
       </c>
@@ -3457,14 +3147,14 @@
         <v>10</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="F53">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -3478,17 +3168,17 @@
         <v>10</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="F54">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>46</v>
       </c>
@@ -3499,17 +3189,17 @@
         <v>48</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="F55">
         <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
         <v>46</v>
       </c>
@@ -3520,17 +3210,17 @@
         <v>49</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="F56">
         <f t="shared" si="0"/>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>46</v>
       </c>
@@ -3541,17 +3231,17 @@
         <v>50</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="F57">
         <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>46</v>
       </c>
@@ -3562,17 +3252,17 @@
         <v>51</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>219</v>
+        <v>168</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="F58">
         <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>46</v>
       </c>
@@ -3583,17 +3273,17 @@
         <v>52</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>222</v>
+        <v>287</v>
       </c>
       <c r="F59">
         <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>46</v>
       </c>
@@ -3604,17 +3294,17 @@
         <v>12</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>223</v>
+        <v>170</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
       <c r="F60">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>46</v>
       </c>
@@ -3625,17 +3315,17 @@
         <v>13</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>225</v>
+        <v>171</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>226</v>
+        <v>289</v>
       </c>
       <c r="F61">
         <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>46</v>
       </c>
@@ -3646,17 +3336,17 @@
         <v>54</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="F62">
         <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>46</v>
       </c>
@@ -3667,17 +3357,17 @@
         <v>55</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="F63">
         <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
         <v>46</v>
       </c>
@@ -3688,17 +3378,17 @@
         <v>48</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="F64">
         <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>46</v>
       </c>
@@ -3709,17 +3399,17 @@
         <v>57</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>233</v>
+        <v>175</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>234</v>
+        <v>293</v>
       </c>
       <c r="F65">
         <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="10" t="s">
         <v>46</v>
       </c>
@@ -3730,17 +3420,17 @@
         <v>58</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>236</v>
+        <v>294</v>
       </c>
       <c r="F66">
         <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="10" t="s">
         <v>46</v>
       </c>
@@ -3751,17 +3441,17 @@
         <v>59</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>237</v>
+        <v>177</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="F67">
         <f t="shared" ref="F67:F118" si="1">LEN(E67)</f>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="10" t="s">
         <v>46</v>
       </c>
@@ -3772,17 +3462,17 @@
         <v>48</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="F68">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="10" t="s">
         <v>46</v>
       </c>
@@ -3793,17 +3483,17 @@
         <v>57</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>241</v>
+        <v>179</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="F69">
         <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="10" t="s">
         <v>46</v>
       </c>
@@ -3814,17 +3504,17 @@
         <v>58</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>243</v>
+        <v>180</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>244</v>
+        <v>298</v>
       </c>
       <c r="F70">
         <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
         <v>46</v>
       </c>
@@ -3835,17 +3525,17 @@
         <v>59</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>246</v>
+        <v>299</v>
       </c>
       <c r="F71">
         <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
         <v>46</v>
       </c>
@@ -3856,17 +3546,17 @@
         <v>62</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>247</v>
+        <v>182</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="F72">
         <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
         <v>46</v>
       </c>
@@ -3877,17 +3567,17 @@
         <v>63</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>249</v>
+        <v>183</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="F73">
         <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
         <v>46</v>
       </c>
@@ -3898,17 +3588,17 @@
         <v>64</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>251</v>
+        <v>184</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>252</v>
+        <v>302</v>
       </c>
       <c r="F74">
         <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="10" t="s">
         <v>46</v>
       </c>
@@ -3919,17 +3609,17 @@
         <v>10</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>253</v>
+        <v>185</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="F75">
         <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>65</v>
       </c>
@@ -3940,17 +3630,17 @@
         <v>67</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>255</v>
+        <v>186</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>344</v>
+        <v>304</v>
       </c>
       <c r="F76">
         <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="10" t="s">
         <v>65</v>
       </c>
@@ -3961,17 +3651,17 @@
         <v>68</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F77">
         <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="10" t="s">
         <v>65</v>
       </c>
@@ -3982,17 +3672,17 @@
         <v>69</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>258</v>
+        <v>188</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="F78">
         <f t="shared" si="1"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="10" t="s">
         <v>65</v>
       </c>
@@ -4003,17 +3693,17 @@
         <v>70</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>260</v>
+        <v>189</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="F79">
         <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="10" t="s">
         <v>65</v>
       </c>
@@ -4024,17 +3714,17 @@
         <v>71</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>262</v>
+        <v>190</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="F80">
         <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="10" t="s">
         <v>65</v>
       </c>
@@ -4045,17 +3735,17 @@
         <v>10</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>265</v>
+        <v>345</v>
       </c>
       <c r="F81">
         <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="10" t="s">
         <v>65</v>
       </c>
@@ -4066,17 +3756,17 @@
         <v>73</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>266</v>
+        <v>192</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>267</v>
+        <v>309</v>
       </c>
       <c r="F82">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="10" t="s">
         <v>65</v>
       </c>
@@ -4087,17 +3777,17 @@
         <v>74</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>268</v>
+        <v>193</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="F83">
         <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="10" t="s">
         <v>65</v>
       </c>
@@ -4108,17 +3798,17 @@
         <v>75</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>270</v>
+        <v>194</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="F84">
         <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
         <v>65</v>
       </c>
@@ -4129,17 +3819,17 @@
         <v>10</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>272</v>
+        <v>195</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>273</v>
+        <v>312</v>
       </c>
       <c r="F85">
         <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="10" t="s">
         <v>65</v>
       </c>
@@ -4150,17 +3840,17 @@
         <v>77</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>274</v>
+        <v>196</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>275</v>
+        <v>313</v>
       </c>
       <c r="F86">
         <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="10" t="s">
         <v>65</v>
       </c>
@@ -4171,17 +3861,17 @@
         <v>78</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>276</v>
+        <v>197</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="F87">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
         <v>65</v>
       </c>
@@ -4192,17 +3882,17 @@
         <v>10</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>278</v>
+        <v>198</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="F88">
         <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="10" t="s">
         <v>65</v>
       </c>
@@ -4213,17 +3903,17 @@
         <v>80</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>280</v>
+        <v>199</v>
       </c>
       <c r="E89" s="18" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="F89">
         <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
         <v>65</v>
       </c>
@@ -4234,17 +3924,17 @@
         <v>81</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>282</v>
+        <v>200</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="F90">
         <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
         <v>65</v>
       </c>
@@ -4255,17 +3945,17 @@
         <v>10</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>284</v>
+        <v>201</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="F91">
         <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
         <v>65</v>
       </c>
@@ -4276,17 +3966,17 @@
         <v>83</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>286</v>
+        <v>202</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="F92">
         <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="10" t="s">
         <v>65</v>
       </c>
@@ -4297,17 +3987,17 @@
         <v>85</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="F93">
         <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="10" t="s">
         <v>65</v>
       </c>
@@ -4318,17 +4008,17 @@
         <v>86</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>290</v>
+        <v>204</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="F94">
         <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="10" t="s">
         <v>65</v>
       </c>
@@ -4339,17 +4029,17 @@
         <v>10</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>292</v>
+        <v>205</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>293</v>
+        <v>322</v>
       </c>
       <c r="F95">
         <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="10" t="s">
         <v>65</v>
       </c>
@@ -4360,17 +4050,17 @@
         <v>88</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>294</v>
+        <v>206</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="F96">
         <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="10" t="s">
         <v>65</v>
       </c>
@@ -4381,17 +4071,17 @@
         <v>51</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>296</v>
+        <v>207</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="F97">
         <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="10" t="s">
         <v>65</v>
       </c>
@@ -4402,17 +4092,17 @@
         <v>10</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>298</v>
+        <v>208</v>
       </c>
       <c r="E98" s="18" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="F98">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="10" t="s">
         <v>65</v>
       </c>
@@ -4423,17 +4113,17 @@
         <v>10</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>300</v>
+        <v>209</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="F99">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="10" t="s">
         <v>89</v>
       </c>
@@ -4444,17 +4134,17 @@
         <v>91</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>302</v>
+        <v>210</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="F100">
         <f t="shared" si="1"/>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="10" t="s">
         <v>89</v>
       </c>
@@ -4465,17 +4155,17 @@
         <v>92</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>304</v>
+        <v>211</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="F101">
         <f t="shared" si="1"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="10" t="s">
         <v>89</v>
       </c>
@@ -4486,17 +4176,17 @@
         <v>93</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>306</v>
+        <v>212</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="F102">
         <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="10" t="s">
         <v>89</v>
       </c>
@@ -4507,17 +4197,17 @@
         <v>10</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>308</v>
+        <v>213</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="F103">
         <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="33" x14ac:dyDescent="0.3">
       <c r="A104" s="10" t="s">
         <v>89</v>
       </c>
@@ -4528,17 +4218,17 @@
         <v>95</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>309</v>
+        <v>214</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="F104">
         <f t="shared" si="1"/>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="10" t="s">
         <v>89</v>
       </c>
@@ -4549,17 +4239,17 @@
         <v>96</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="F105">
         <f t="shared" si="1"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="10" t="s">
         <v>89</v>
       </c>
@@ -4570,17 +4260,17 @@
         <v>10</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>313</v>
+        <v>216</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="F106">
         <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="10" t="s">
         <v>89</v>
       </c>
@@ -4591,17 +4281,17 @@
         <v>10</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>315</v>
+        <v>217</v>
       </c>
       <c r="E107" s="18" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="F107">
         <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="10" t="s">
         <v>10</v>
       </c>
@@ -4612,17 +4302,17 @@
         <v>97</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>317</v>
+        <v>218</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="F108">
         <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="10" t="s">
         <v>10</v>
       </c>
@@ -4633,17 +4323,17 @@
         <v>10</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>319</v>
+        <v>219</v>
       </c>
       <c r="E109" s="18" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="F109">
         <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="10" t="s">
         <v>10</v>
       </c>
@@ -4654,17 +4344,17 @@
         <v>99</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>321</v>
+        <v>220</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="F110">
         <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="10" t="s">
         <v>10</v>
       </c>
@@ -4675,17 +4365,17 @@
         <v>10</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>323</v>
+        <v>221</v>
       </c>
       <c r="E111" s="18" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="F111">
         <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="10" t="s">
         <v>10</v>
       </c>
@@ -4696,17 +4386,17 @@
         <v>101</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>325</v>
+        <v>222</v>
       </c>
       <c r="E112" s="18" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="F112">
         <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="10" t="s">
         <v>10</v>
       </c>
@@ -4717,17 +4407,17 @@
         <v>102</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>327</v>
+        <v>223</v>
       </c>
       <c r="E113" s="18" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="F113">
         <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="10" t="s">
         <v>10</v>
       </c>
@@ -4738,17 +4428,17 @@
         <v>10</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>329</v>
+        <v>224</v>
       </c>
       <c r="E114" s="18" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="F114">
         <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="10" t="s">
         <v>10</v>
       </c>
@@ -4759,17 +4449,17 @@
         <v>104</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>331</v>
+        <v>225</v>
       </c>
       <c r="E115" s="18" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="F115">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
         <v>10</v>
       </c>
@@ -4780,17 +4470,17 @@
         <v>105</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>333</v>
+        <v>226</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F116">
         <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="10" t="s">
         <v>10</v>
       </c>
@@ -4801,14 +4491,14 @@
         <v>10</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>335</v>
+        <v>227</v>
       </c>
       <c r="E117" s="18" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F117">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4822,14 +4512,14 @@
         <v>10</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="F118">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/service_group.xlsx
+++ b/service_group.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\상수\Desktop\서비스자원검색\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\정상수\Desktop\서비스자원검색(260318)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13965"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13968"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1038,10 +1038,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>치아 상태 확인 필요, 거동 불편으로 치과 방문 어려워 집에서 구강 상태 점검 희망</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>방문 구강 관리 포함 치아 관리 서비스 상담 및 이용 가능 여부 문의</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -1327,6 +1323,10 @@
   </si>
   <si>
     <t>일상생활 지원 서비스 상담 및 생활 돌봄 서비스 이용 희망</t>
+  </si>
+  <si>
+    <t>치아 상태 확인 필요, 집에서 구강 상태 점검 희망, 잇몸출혈, 입냄새, 양치 어려움</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2034,17 +2034,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I118"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="102.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="100.625" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.69921875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="102.8984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="100.59765625" style="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="10" t="s">
         <v>2</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
         <v>2</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="10" t="s">
         <v>2</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="10" t="s">
         <v>2</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="10" t="s">
         <v>2</v>
       </c>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="10" t="s">
         <v>2</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
         <v>2</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="10" t="s">
         <v>2</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="10" t="s">
         <v>2</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="10" t="s">
         <v>2</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="s">
         <v>2</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
         <v>2</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
         <v>2</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
         <v>2</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
         <v>2</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="10" t="s">
         <v>2</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
         <v>2</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="10" t="s">
         <v>2</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="10" t="s">
         <v>23</v>
       </c>
@@ -2520,14 +2520,14 @@
         <v>133</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>252</v>
+        <v>345</v>
       </c>
       <c r="F23">
         <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>23</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>23</v>
       </c>
@@ -2562,14 +2562,14 @@
         <v>135</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>23</v>
       </c>
@@ -2583,14 +2583,14 @@
         <v>136</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F26">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="10" t="s">
         <v>23</v>
       </c>
@@ -2604,14 +2604,14 @@
         <v>137</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F27">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="10" t="s">
         <v>23</v>
       </c>
@@ -2625,14 +2625,14 @@
         <v>138</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F28">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
         <v>23</v>
       </c>
@@ -2646,14 +2646,14 @@
         <v>139</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F29">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="10" t="s">
         <v>23</v>
       </c>
@@ -2667,14 +2667,14 @@
         <v>140</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F30">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="10" t="s">
         <v>23</v>
       </c>
@@ -2688,14 +2688,14 @@
         <v>141</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F31">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="10" t="s">
         <v>23</v>
       </c>
@@ -2709,14 +2709,14 @@
         <v>142</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F32">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="10" t="s">
         <v>23</v>
       </c>
@@ -2730,14 +2730,14 @@
         <v>143</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F33">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
         <v>23</v>
       </c>
@@ -2751,14 +2751,14 @@
         <v>144</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F34">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="10" t="s">
         <v>23</v>
       </c>
@@ -2772,14 +2772,14 @@
         <v>145</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F35">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="10" t="s">
         <v>23</v>
       </c>
@@ -2793,14 +2793,14 @@
         <v>146</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F36">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="10" t="s">
         <v>23</v>
       </c>
@@ -2814,14 +2814,14 @@
         <v>147</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F37">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
         <v>23</v>
       </c>
@@ -2835,14 +2835,14 @@
         <v>148</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="10" t="s">
         <v>23</v>
       </c>
@@ -2856,14 +2856,14 @@
         <v>149</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F39">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="10" t="s">
         <v>23</v>
       </c>
@@ -2877,14 +2877,14 @@
         <v>150</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F40">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="10" t="s">
         <v>23</v>
       </c>
@@ -2898,14 +2898,14 @@
         <v>151</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F41">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="10" t="s">
         <v>23</v>
       </c>
@@ -2919,14 +2919,14 @@
         <v>152</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F42">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="10" t="s">
         <v>23</v>
       </c>
@@ -2940,14 +2940,14 @@
         <v>153</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F43">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="10" t="s">
         <v>23</v>
       </c>
@@ -2961,14 +2961,14 @@
         <v>154</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F44">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="10" t="s">
         <v>23</v>
       </c>
@@ -2982,14 +2982,14 @@
         <v>155</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F45">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" s="10" t="s">
         <v>23</v>
       </c>
@@ -3003,14 +3003,14 @@
         <v>156</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F46">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="10" t="s">
         <v>23</v>
       </c>
@@ -3024,14 +3024,14 @@
         <v>157</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F47">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="10" t="s">
         <v>23</v>
       </c>
@@ -3045,14 +3045,14 @@
         <v>159</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F48">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="10" t="s">
         <v>23</v>
       </c>
@@ -3066,14 +3066,14 @@
         <v>160</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F49">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="10" t="s">
         <v>23</v>
       </c>
@@ -3087,14 +3087,14 @@
         <v>161</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F50">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="10" t="s">
         <v>23</v>
       </c>
@@ -3108,14 +3108,14 @@
         <v>158</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F51">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="10" t="s">
         <v>23</v>
       </c>
@@ -3129,14 +3129,14 @@
         <v>162</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F52">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="10" t="s">
         <v>23</v>
       </c>
@@ -3150,14 +3150,14 @@
         <v>163</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F53">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" s="10" t="s">
         <v>23</v>
       </c>
@@ -3171,14 +3171,14 @@
         <v>164</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F54">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55" s="10" t="s">
         <v>46</v>
       </c>
@@ -3192,14 +3192,14 @@
         <v>165</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F55">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56" s="10" t="s">
         <v>46</v>
       </c>
@@ -3213,14 +3213,14 @@
         <v>166</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F56">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57" s="10" t="s">
         <v>46</v>
       </c>
@@ -3234,14 +3234,14 @@
         <v>167</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F57">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58" s="10" t="s">
         <v>46</v>
       </c>
@@ -3255,14 +3255,14 @@
         <v>168</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F58">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59" s="10" t="s">
         <v>46</v>
       </c>
@@ -3276,14 +3276,14 @@
         <v>169</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F59">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60" s="10" t="s">
         <v>46</v>
       </c>
@@ -3297,14 +3297,14 @@
         <v>170</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F60">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61" s="10" t="s">
         <v>46</v>
       </c>
@@ -3318,14 +3318,14 @@
         <v>171</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F61">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62" s="10" t="s">
         <v>46</v>
       </c>
@@ -3339,14 +3339,14 @@
         <v>172</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F62">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63" s="10" t="s">
         <v>46</v>
       </c>
@@ -3360,14 +3360,14 @@
         <v>173</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F63">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64" s="10" t="s">
         <v>46</v>
       </c>
@@ -3381,14 +3381,14 @@
         <v>174</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F64">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65" s="10" t="s">
         <v>46</v>
       </c>
@@ -3402,14 +3402,14 @@
         <v>175</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66" s="10" t="s">
         <v>46</v>
       </c>
@@ -3423,14 +3423,14 @@
         <v>176</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F66">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" s="10" t="s">
         <v>46</v>
       </c>
@@ -3444,14 +3444,14 @@
         <v>177</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F67">
         <f t="shared" ref="F67:F118" si="1">LEN(E67)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" s="10" t="s">
         <v>46</v>
       </c>
@@ -3465,14 +3465,14 @@
         <v>178</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F68">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69" s="10" t="s">
         <v>46</v>
       </c>
@@ -3486,14 +3486,14 @@
         <v>179</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F69">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70" s="10" t="s">
         <v>46</v>
       </c>
@@ -3507,14 +3507,14 @@
         <v>180</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F70">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71" s="10" t="s">
         <v>46</v>
       </c>
@@ -3528,14 +3528,14 @@
         <v>181</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F71">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" s="10" t="s">
         <v>46</v>
       </c>
@@ -3549,14 +3549,14 @@
         <v>182</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F72">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" s="10" t="s">
         <v>46</v>
       </c>
@@ -3570,14 +3570,14 @@
         <v>183</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F73">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" s="10" t="s">
         <v>46</v>
       </c>
@@ -3591,14 +3591,14 @@
         <v>184</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F74">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" s="10" t="s">
         <v>46</v>
       </c>
@@ -3612,14 +3612,14 @@
         <v>185</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F75">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" s="10" t="s">
         <v>65</v>
       </c>
@@ -3633,14 +3633,14 @@
         <v>186</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F76">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77" s="10" t="s">
         <v>65</v>
       </c>
@@ -3654,14 +3654,14 @@
         <v>187</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F77">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78" s="10" t="s">
         <v>65</v>
       </c>
@@ -3675,14 +3675,14 @@
         <v>188</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F78">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" s="10" t="s">
         <v>65</v>
       </c>
@@ -3696,14 +3696,14 @@
         <v>189</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F79">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80" s="10" t="s">
         <v>65</v>
       </c>
@@ -3717,14 +3717,14 @@
         <v>190</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F80">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81" s="10" t="s">
         <v>65</v>
       </c>
@@ -3738,14 +3738,14 @@
         <v>191</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F81">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82" s="10" t="s">
         <v>65</v>
       </c>
@@ -3759,14 +3759,14 @@
         <v>192</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F82">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83" s="10" t="s">
         <v>65</v>
       </c>
@@ -3780,14 +3780,14 @@
         <v>193</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F83">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84" s="10" t="s">
         <v>65</v>
       </c>
@@ -3801,14 +3801,14 @@
         <v>194</v>
       </c>
       <c r="E84" s="18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F84">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85" s="10" t="s">
         <v>65</v>
       </c>
@@ -3822,14 +3822,14 @@
         <v>195</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F85">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86" s="10" t="s">
         <v>65</v>
       </c>
@@ -3843,14 +3843,14 @@
         <v>196</v>
       </c>
       <c r="E86" s="18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F86">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A87" s="10" t="s">
         <v>65</v>
       </c>
@@ -3864,14 +3864,14 @@
         <v>197</v>
       </c>
       <c r="E87" s="18" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F87">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88" s="10" t="s">
         <v>65</v>
       </c>
@@ -3885,14 +3885,14 @@
         <v>198</v>
       </c>
       <c r="E88" s="18" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F88">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89" s="10" t="s">
         <v>65</v>
       </c>
@@ -3906,14 +3906,14 @@
         <v>199</v>
       </c>
       <c r="E89" s="18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F89">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90" s="10" t="s">
         <v>65</v>
       </c>
@@ -3927,14 +3927,14 @@
         <v>200</v>
       </c>
       <c r="E90" s="18" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F90">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91" s="10" t="s">
         <v>65</v>
       </c>
@@ -3948,14 +3948,14 @@
         <v>201</v>
       </c>
       <c r="E91" s="18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F91">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92" s="10" t="s">
         <v>65</v>
       </c>
@@ -3969,14 +3969,14 @@
         <v>202</v>
       </c>
       <c r="E92" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F92">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93" s="10" t="s">
         <v>65</v>
       </c>
@@ -3990,14 +3990,14 @@
         <v>203</v>
       </c>
       <c r="E93" s="18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F93">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94" s="10" t="s">
         <v>65</v>
       </c>
@@ -4011,14 +4011,14 @@
         <v>204</v>
       </c>
       <c r="E94" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F94">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95" s="10" t="s">
         <v>65</v>
       </c>
@@ -4032,14 +4032,14 @@
         <v>205</v>
       </c>
       <c r="E95" s="18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F95">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A96" s="10" t="s">
         <v>65</v>
       </c>
@@ -4053,14 +4053,14 @@
         <v>206</v>
       </c>
       <c r="E96" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F96">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97" s="10" t="s">
         <v>65</v>
       </c>
@@ -4074,14 +4074,14 @@
         <v>207</v>
       </c>
       <c r="E97" s="18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F97">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A98" s="10" t="s">
         <v>65</v>
       </c>
@@ -4095,14 +4095,14 @@
         <v>208</v>
       </c>
       <c r="E98" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F98">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A99" s="10" t="s">
         <v>65</v>
       </c>
@@ -4116,14 +4116,14 @@
         <v>209</v>
       </c>
       <c r="E99" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F99">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A100" s="10" t="s">
         <v>89</v>
       </c>
@@ -4137,14 +4137,14 @@
         <v>210</v>
       </c>
       <c r="E100" s="18" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F100">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A101" s="10" t="s">
         <v>89</v>
       </c>
@@ -4158,14 +4158,14 @@
         <v>211</v>
       </c>
       <c r="E101" s="18" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F101">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102" s="10" t="s">
         <v>89</v>
       </c>
@@ -4179,14 +4179,14 @@
         <v>212</v>
       </c>
       <c r="E102" s="18" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F102">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A103" s="10" t="s">
         <v>89</v>
       </c>
@@ -4200,14 +4200,14 @@
         <v>213</v>
       </c>
       <c r="E103" s="18" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F103">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" ht="34.799999999999997" x14ac:dyDescent="0.4">
       <c r="A104" s="10" t="s">
         <v>89</v>
       </c>
@@ -4221,14 +4221,14 @@
         <v>214</v>
       </c>
       <c r="E104" s="18" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F104">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A105" s="10" t="s">
         <v>89</v>
       </c>
@@ -4242,14 +4242,14 @@
         <v>215</v>
       </c>
       <c r="E105" s="18" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F105">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A106" s="10" t="s">
         <v>89</v>
       </c>
@@ -4263,14 +4263,14 @@
         <v>216</v>
       </c>
       <c r="E106" s="18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F106">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107" s="10" t="s">
         <v>89</v>
       </c>
@@ -4284,14 +4284,14 @@
         <v>217</v>
       </c>
       <c r="E107" s="18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F107">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A108" s="10" t="s">
         <v>10</v>
       </c>
@@ -4305,14 +4305,14 @@
         <v>218</v>
       </c>
       <c r="E108" s="18" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F108">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A109" s="10" t="s">
         <v>10</v>
       </c>
@@ -4326,14 +4326,14 @@
         <v>219</v>
       </c>
       <c r="E109" s="18" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F109">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A110" s="10" t="s">
         <v>10</v>
       </c>
@@ -4347,14 +4347,14 @@
         <v>220</v>
       </c>
       <c r="E110" s="18" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F110">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A111" s="10" t="s">
         <v>10</v>
       </c>
@@ -4368,14 +4368,14 @@
         <v>221</v>
       </c>
       <c r="E111" s="18" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F111">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A112" s="10" t="s">
         <v>10</v>
       </c>
@@ -4389,14 +4389,14 @@
         <v>222</v>
       </c>
       <c r="E112" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F112">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A113" s="10" t="s">
         <v>10</v>
       </c>
@@ -4410,14 +4410,14 @@
         <v>223</v>
       </c>
       <c r="E113" s="18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F113">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A114" s="10" t="s">
         <v>10</v>
       </c>
@@ -4431,14 +4431,14 @@
         <v>224</v>
       </c>
       <c r="E114" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F114">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A115" s="10" t="s">
         <v>10</v>
       </c>
@@ -4452,14 +4452,14 @@
         <v>225</v>
       </c>
       <c r="E115" s="18" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F115">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A116" s="10" t="s">
         <v>10</v>
       </c>
@@ -4473,14 +4473,14 @@
         <v>226</v>
       </c>
       <c r="E116" s="18" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F116">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A117" s="10" t="s">
         <v>10</v>
       </c>
@@ -4494,14 +4494,14 @@
         <v>227</v>
       </c>
       <c r="E117" s="18" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F117">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A118" s="14" t="s">
         <v>10</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>228</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F118">
         <f t="shared" si="1"/>
